--- a/Productos.xlsx
+++ b/Productos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenovo\Desktop\Productos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FF85A22-4854-4026-B865-21811968C132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ED5B3C0-8A46-4FBE-87EF-F8E9BDDD305D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{26820DB9-924D-46B1-8890-C9E1FF544FE7}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="90">
   <si>
     <t>Sueter algodón cuello redondo</t>
   </si>
@@ -195,9 +195,6 @@
     <t>Costo reproceso</t>
   </si>
   <si>
-    <t>Única</t>
-  </si>
-  <si>
     <t>5.35cmx3.15cm</t>
   </si>
   <si>
@@ -270,9 +267,6 @@
     <t>Blusa-001-G-F.png</t>
   </si>
   <si>
-    <t>Blusa-001-V-F.png</t>
-  </si>
-  <si>
     <t>Blusa-001-C-F.png</t>
   </si>
   <si>
@@ -297,7 +291,10 @@
     <t>Bandera-001.png</t>
   </si>
   <si>
-    <t>Tula-001.png</t>
+    <t>Blusa-001-VT-F.png</t>
+  </si>
+  <si>
+    <t>Tula-001.jpeg</t>
   </si>
 </sst>
 </file>
@@ -692,10 +689,10 @@
         <v>9</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>60</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -733,10 +730,10 @@
         <v>22</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>0</v>
@@ -751,7 +748,7 @@
         <v>17</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I2" s="2">
         <v>10</v>
@@ -774,10 +771,10 @@
         <v>23</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>0</v>
@@ -792,7 +789,7 @@
         <v>17</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I3" s="2">
         <v>3</v>
@@ -815,10 +812,10 @@
         <v>24</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>14</v>
@@ -833,7 +830,7 @@
         <v>17</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I4" s="2">
         <v>1</v>
@@ -856,10 +853,10 @@
         <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>14</v>
@@ -874,7 +871,7 @@
         <v>17</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I5" s="2">
         <v>1</v>
@@ -897,10 +894,10 @@
         <v>26</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>14</v>
@@ -915,7 +912,7 @@
         <v>17</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I6" s="2">
         <v>1</v>
@@ -938,10 +935,10 @@
         <v>27</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>14</v>
@@ -956,7 +953,7 @@
         <v>17</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I7" s="2">
         <v>1</v>
@@ -979,10 +976,10 @@
         <v>31</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>0</v>
@@ -997,7 +994,7 @@
         <v>21</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I8" s="2">
         <v>0</v>
@@ -1020,10 +1017,10 @@
         <v>31</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>0</v>
@@ -1038,7 +1035,7 @@
         <v>21</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I9" s="2">
         <v>5</v>
@@ -1061,10 +1058,10 @@
         <v>33</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>1</v>
@@ -1079,7 +1076,7 @@
         <v>21</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I10" s="2">
         <v>3</v>
@@ -1101,10 +1098,10 @@
         <v>32</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>1</v>
@@ -1119,7 +1116,7 @@
         <v>21</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I11" s="2">
         <v>3</v>
@@ -1141,10 +1138,10 @@
         <v>35</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>1</v>
@@ -1159,7 +1156,7 @@
         <v>21</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I12" s="2">
         <v>2</v>
@@ -1181,10 +1178,10 @@
         <v>34</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>1</v>
@@ -1199,7 +1196,7 @@
         <v>21</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I13" s="2">
         <v>2</v>
@@ -1221,7 +1218,7 @@
         <v>42</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>18</v>
@@ -1239,7 +1236,7 @@
         <v>21</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I14" s="2">
         <v>1</v>
@@ -1262,7 +1259,7 @@
         <v>46</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>18</v>
@@ -1280,7 +1277,7 @@
         <v>21</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I15" s="2">
         <v>1</v>
@@ -1303,7 +1300,7 @@
         <v>43</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>18</v>
@@ -1321,7 +1318,7 @@
         <v>21</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I16" s="2">
         <v>1</v>
@@ -1344,7 +1341,7 @@
         <v>44</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>18</v>
@@ -1362,7 +1359,7 @@
         <v>21</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="I17" s="2">
         <v>1</v>
@@ -1385,7 +1382,7 @@
         <v>45</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>18</v>
@@ -1403,7 +1400,7 @@
         <v>21</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="I18" s="2">
         <v>1</v>
@@ -1426,7 +1423,7 @@
         <v>39</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>20</v>
@@ -1438,10 +1435,10 @@
         <v>41</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I19" s="2">
         <v>2</v>
@@ -1463,7 +1460,7 @@
         <v>40</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>19</v>
@@ -1478,7 +1475,7 @@
         <v>54</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I20" s="2">
         <v>10</v>
@@ -1501,22 +1498,19 @@
         <v>47</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>48</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F21" s="2" t="s">
-        <v>56</v>
-      </c>
       <c r="H21" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I21" s="2">
         <v>1</v>
@@ -1539,22 +1533,19 @@
         <v>49</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>48</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F22" s="2" t="s">
-        <v>56</v>
-      </c>
       <c r="H22" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I22" s="2">
         <v>1</v>
@@ -1577,22 +1568,19 @@
         <v>50</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>48</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F23" s="2" t="s">
-        <v>56</v>
-      </c>
       <c r="H23" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I23" s="2">
         <v>1</v>
@@ -1615,22 +1603,19 @@
         <v>51</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>48</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F24" s="2" t="s">
-        <v>56</v>
-      </c>
       <c r="H24" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I24" s="2">
         <v>1</v>
@@ -1653,22 +1638,19 @@
         <v>52</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>48</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F25" s="2" t="s">
-        <v>56</v>
-      </c>
       <c r="H25" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I25" s="2">
         <v>1</v>
@@ -1688,22 +1670,22 @@
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C26" s="2" t="s">
+      <c r="D26" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="F26" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F26" s="2" t="s">
-        <v>68</v>
-      </c>
       <c r="H26" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="I26" s="2">
         <v>3</v>
